--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/WASHINGTON_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/WASHINGTON_2022.xlsx
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C178">
@@ -3955,7 +3955,7 @@
         <v>41</v>
       </c>
       <c r="D200">
-        <v>0.009105041083721963</v>
+        <v>0.009105041083721965</v>
       </c>
     </row>
     <row r="201">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C569">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C570">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C602">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C603">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C606">
